--- a/stories/arbres/TREE-DIF-007.xlsx
+++ b/stories/arbres/TREE-DIF-007.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nino est à l'école, avec maman. Papa viendra plus tard. Un camarade a besoin de calme. Il regarde d'abord. Maman dit : on peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>Nino est à l'école, avec maman. Papa viendra plus tard. Un camarade a besoin de calme. Il regarde d'abord. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,12 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Nino est à l'école, avec maman. Papa viendra plus tard. Un camarade a besoin de calme. Il regarde d'abord.
+maman|On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1510,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1539,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>À l'école, il y a un coin chat. Un camarade reste au bord. Nino répète la règle : on touche tout doux. On peut observer d'abord. Le camarade regarde. Maman dit : c'est bien. On peut jouer ensemble.</t>
+          <t>À l'école, il y a un coin chat. Un camarade reste au bord. Nino répète la règle : on touche tout doux. On peut observer d'abord. Le camarade regarde. C'est bien. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1677,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|À l'école, il y a un coin chat. Un camarade reste au bord. Nino répète la règle : on touche tout doux. On peut observer d'abord. Le camarade regarde.
+maman|C'est bien. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1859,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On répète la règle ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2032,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On peut répéter. On peut observer d'abord. Nino respire. Maman est là. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2223,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2390,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers le bac à sable. Il répète la règle : on reste assis. Un camarade observe d'abord. Le chat en peluche est là. Maman montre le geste, lentement. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2529,6 +2583,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -2693,6 +2752,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi le chat. Puis le bac à sable. Puis rouge. Un chat miaule une fois. Nino range la tasse. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2919,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3086,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Nino s'arrête près de bleu. le bac à sable est rangé. Un panier est posé sur le banc. Nino souffle, puis sourit à maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3253,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3420,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Nino se souvient de le chat. Et de le bac à sable. Et de vert. L'eau coule, tout petit bruit. Nino essuie ses mains. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3587,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3527,7 +3616,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Nino va vers le toboggan. Il répète la règle : un à la fois. Un camarade observe d'abord. Le chat en peluche attend. Maman dit : je suis là. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>Nino va vers le toboggan. Il répète la règle : un à la fois. Un camarade observe d'abord. Le chat en peluche attend. Je suis là. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3665,6 +3754,12 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers le toboggan. Il répète la règle : un à la fois. Un camarade observe d'abord. Le chat en peluche attend.
+maman|Je suis là. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3853,6 +3948,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -4017,6 +4117,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Avec rouge. Après le toboggan. Près de le chat. Nino s'arrête. Un linge sèche à l'air. Nino range encore un peu, près de maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4284,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4451,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Nino range le toboggan. bleu reste près de le chat. On écoute jusqu'au bout. Papa n'est pas loin. Nino les rejoint. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4618,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4527,7 +4647,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>vert est là. le toboggan aussi. le chat reste dans le souvenir. Une feuille tombe. Nino chuchote : c'est fini. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Vert est là. le toboggan aussi. le chat reste dans le souvenir. Une feuille tombe. Nino chuchote : c'est fini. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4665,6 +4785,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Vert est là. le toboggan aussi. le chat reste dans le souvenir. Une feuille tombe. Nino chuchote : c'est fini. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4952,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5119,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers les balançoires. Il répète la règle : on s'arrête. Un camarade observe d'abord. Le chat en peluche est sur le banc. Maman reste tout près. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5177,6 +5312,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -5341,6 +5481,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint rouge. les balançoires est rangé. le chat est fini. La lumière est claire. Nino s'assoit près de maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5648,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5815,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Près de bleu. Nino pose les balançoires. le chat est derrière. On attend son tour. Nino pose les balançoires à sa place. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5982,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6149,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Nino montre vert. Maman a vu le chat. Et les balançoires. Un ballon s'immobilise. Nino ferme le sac. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6316,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6313,6 +6483,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|À l'école, il y a un coin chien en images. Un camarade a besoin de calme. Nino répète la règle. On peut observer d'abord. Le camarade respire. Puis il s'approche. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6493,6 +6668,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On peut observer d'abord ?</t>
         </is>
       </c>
     </row>
@@ -6661,6 +6841,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On peut répéter. On peut observer d'abord. Nino retient le geste. Maman sourit. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6847,6 +7032,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6871,7 +7061,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Nino va vers le bac à sable. Il répète la règle. Un camarade observe d'abord. L'image du chien est collée au seau. Maman dit : je suis là. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>Nino va vers le bac à sable. Il répète la règle. Un camarade observe d'abord. L'image du chien est collée au seau. Je suis là. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7009,6 +7199,12 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers le bac à sable. Il répète la règle. Un camarade observe d'abord. L'image du chien est collée au seau.
+maman|Je suis là. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7197,6 +7393,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -7361,6 +7562,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi le chien. Puis le bac à sable. Puis rouge. Une chaussette est encore sablée. Nino écoute maman encore une fois. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7523,6 +7729,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7685,6 +7896,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Nino s'arrête près de bleu. le bac à sable est rangé. On souffle doucement. Nino marche près de maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7847,6 +8063,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8009,6 +8230,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Nino se souvient de le chien. Et de le bac à sable. Et de vert. Un galet est encore chaud. Nino range le chien dans sa tête, comme un souvenir. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8171,6 +8397,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8333,6 +8564,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers le toboggan. Il répète la règle. Un camarade observe d'abord. L'image du chien est sur la rampe. Maman reste tout près. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8521,6 +8757,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -8685,6 +8926,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Avec rouge. Après le toboggan. Près de le chien. Nino s'arrête. Une tasse cliquette. Nino tend rouge à papa. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8847,6 +9093,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9009,6 +9260,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Nino range le toboggan. bleu reste près de le chien. Un ruban reste dans la poche. Nino dit merci à maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9171,6 +9427,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9195,7 +9456,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>vert est là. le toboggan aussi. le chien reste dans le souvenir. Le sol est un peu froid. Nino enfile ses chaussons. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Vert est là. le toboggan aussi. le chien reste dans le souvenir. Le sol est un peu froid. Nino enfile ses chaussons. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9333,6 +9594,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Vert est là. le toboggan aussi. le chien reste dans le souvenir. Le sol est un peu froid. Nino enfile ses chaussons. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9495,6 +9761,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9657,6 +9928,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers les balançoires. Il répète la règle. Un camarade observe d'abord. L'image du chien bouge un peu. Maman montre le geste, lentement. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9845,6 +10121,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -10009,6 +10290,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint rouge. les balançoires est rangé. le chien est fini. On se tient la main. Nino plie un pull. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10171,6 +10457,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10333,6 +10624,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Près de bleu. Nino pose les balançoires. le chien est derrière. Le vent est doux. Nino caresse le doudou. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10495,6 +10791,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10657,6 +10958,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Nino montre vert. Maman a vu le chien. Et les balançoires. On dit merci. Nino pose sa tête un moment. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10819,6 +11125,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10981,6 +11292,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|À l'école, on parle de la poule de la ferme. Un camarade n'entre pas tout de suite. Nino répète la règle. On peut observer d'abord. Papa arrivera plus tard. On attend. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11157,6 +11473,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On force, ou on répète ?</t>
         </is>
       </c>
     </row>
@@ -11325,6 +11646,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On peut répéter. On peut observer d'abord. Nino hoche la tête. On continue, avec maman. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11511,6 +11837,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11673,6 +12004,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers le bac à sable. Il répète la règle. Un camarade observe d'abord. On parle de la poule, tout doux. Maman reste tout près. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11861,6 +12197,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -12025,6 +12366,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi la poule. Puis le bac à sable. Puis rouge. Les chaussures font toc toc. Nino prend la main de maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12187,6 +12533,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12349,6 +12700,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Nino s'arrête près de bleu. le bac à sable est rangé. Une pomme brille un peu. Nino sourit. Maman sourit aussi. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12511,6 +12867,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12673,6 +13034,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Nino se souvient de la poule. Et de le bac à sable. Et de vert. Un vélo passe au loin. Nino répète tout bas le geste. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12835,6 +13201,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12997,6 +13368,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers le toboggan. Il répète la règle. Un camarade observe d'abord. On parle de la poule, tout doux. Maman montre le geste, lentement. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13185,6 +13561,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -13349,6 +13730,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Avec rouge. Après le toboggan. Près de la poule. Nino s'arrête. Il y a des miettes sur la table. Nino raccroche un linge. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13511,6 +13897,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13673,6 +14064,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Nino range le toboggan. bleu reste près de la poule. Le savon sent bon. Nino montre bleu à maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13835,6 +14231,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13859,7 +14260,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>vert est là. le toboggan aussi. la poule reste dans le souvenir. On rit un peu. Nino boit une gorgée d'eau. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Vert est là. le toboggan aussi. la poule reste dans le souvenir. On rit un peu. Nino boit une gorgée d'eau. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13997,6 +14398,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Vert est là. le toboggan aussi. la poule reste dans le souvenir. On rit un peu. Nino boit une gorgée d'eau. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14159,6 +14565,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14183,7 +14594,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Nino va vers les balançoires. Il répète la règle. Un camarade observe d'abord. On parle de la poule, tout doux. Maman dit : je suis là. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>Nino va vers les balançoires. Il répète la règle. Un camarade observe d'abord. On parle de la poule, tout doux. Je suis là. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14321,6 +14732,12 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Nino va vers les balançoires. Il répète la règle. Un camarade observe d'abord. On parle de la poule, tout doux.
+maman|Je suis là. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14509,6 +14926,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -14673,6 +15095,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rejoint rouge. les balançoires est rangé. la poule est fini. Une cloche tinte, tout loin. Nino serre la main de maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14835,6 +15262,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14859,7 +15291,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Près de bleu. Nino pose les balançoires. la poule est derrière. La couverture est douce. Nino dit : j'ai appris. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Près de bleu. Nino pose les balançoires. la poule est derrière. La couverture est douce. J'ai appris. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -14997,6 +15429,13 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Près de bleu. Nino pose les balançoires. la poule est derrière. La couverture est douce.
+enfant-m|J'ai appris. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord.
+narrateur|Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15159,6 +15598,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15321,6 +15765,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Nino montre vert. Maman a vu la poule. Et les balançoires. Ça sent le pain chaud. Nino ferme la porte, tout doux. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15483,6 +15932,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15501,7 +15955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15574,6 +16028,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-007.xlsx
+++ b/stories/arbres/TREE-DIF-007.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1324,6 +1329,7 @@
 maman|On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1513,6 +1519,11 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -1683,6 +1694,7 @@
 maman|C'est bien. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1866,6 +1878,7 @@
           <t>narrateur|On répète la règle ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2037,6 +2050,7 @@
           <t>narrateur|Oui. On peut répéter. On peut observer d'abord. Nino respire. Maman est là. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2228,6 +2242,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2395,6 +2410,7 @@
           <t>narrateur|Nino va vers le bac à sable. Il répète la règle : on reste assis. Un camarade observe d'abord. Le chat en peluche est là. Maman montre le geste, lentement. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2590,6 +2606,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2757,6 +2774,7 @@
           <t>narrateur|Nino a choisi le chat. Puis le bac à sable. Puis rouge. Un chat miaule une fois. Nino range la tasse. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2924,6 +2942,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3091,6 +3110,7 @@
           <t>narrateur|Nino s'arrête près de bleu. le bac à sable est rangé. Un panier est posé sur le banc. Nino souffle, puis sourit à maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3258,6 +3278,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3425,6 +3446,7 @@
           <t>narrateur|Nino se souvient de le chat. Et de le bac à sable. Et de vert. L'eau coule, tout petit bruit. Nino essuie ses mains. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3592,6 +3614,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3760,6 +3783,7 @@
 maman|Je suis là. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3955,6 +3979,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4122,6 +4147,7 @@
           <t>narrateur|Avec rouge. Après le toboggan. Près de le chat. Nino s'arrête. Un linge sèche à l'air. Nino range encore un peu, près de maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4289,6 +4315,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4456,6 +4483,7 @@
           <t>narrateur|Nino range le toboggan. bleu reste près de le chat. On écoute jusqu'au bout. Papa n'est pas loin. Nino les rejoint. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4623,6 +4651,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4790,6 +4819,7 @@
           <t>narrateur|Vert est là. le toboggan aussi. le chat reste dans le souvenir. Une feuille tombe. Nino chuchote : c'est fini. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4957,6 +4987,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5124,6 +5155,7 @@
           <t>narrateur|Nino va vers les balançoires. Il répète la règle : on s'arrête. Un camarade observe d'abord. Le chat en peluche est sur le banc. Maman reste tout près. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5319,6 +5351,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5486,6 +5519,7 @@
           <t>narrateur|Nino rejoint rouge. les balançoires est rangé. le chat est fini. La lumière est claire. Nino s'assoit près de maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5653,6 +5687,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5820,6 +5855,7 @@
           <t>narrateur|Près de bleu. Nino pose les balançoires. le chat est derrière. On attend son tour. Nino pose les balançoires à sa place. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5987,6 +6023,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6154,6 +6191,7 @@
           <t>narrateur|Nino montre vert. Maman a vu le chat. Et les balançoires. Un ballon s'immobilise. Nino ferme le sac. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6321,6 +6359,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6488,6 +6527,11 @@
           <t>narrateur|À l'école, il y a un coin chien en images. Un camarade a besoin de calme. Nino répète la règle. On peut observer d'abord. Le camarade respire. Puis il s'approche. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6675,6 +6719,7 @@
           <t>narrateur|On peut observer d'abord ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6846,6 +6891,7 @@
           <t>narrateur|Oui. On peut répéter. On peut observer d'abord. Nino retient le geste. Maman sourit. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7037,6 +7083,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7205,6 +7252,11 @@
 maman|Je suis là. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7400,6 +7452,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7567,6 +7620,11 @@
           <t>narrateur|Nino a choisi le chien. Puis le bac à sable. Puis rouge. Une chaussette est encore sablée. Nino écoute maman encore une fois. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7734,6 +7792,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7901,6 +7960,7 @@
           <t>narrateur|Nino s'arrête près de bleu. le bac à sable est rangé. On souffle doucement. Nino marche près de maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8068,6 +8128,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8235,6 +8296,11 @@
           <t>narrateur|Nino se souvient de le chien. Et de le bac à sable. Et de vert. Un galet est encore chaud. Nino range le chien dans sa tête, comme un souvenir. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8402,6 +8468,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8569,6 +8636,11 @@
           <t>narrateur|Nino va vers le toboggan. Il répète la règle. Un camarade observe d'abord. L'image du chien est sur la rampe. Maman reste tout près. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8764,6 +8836,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8931,6 +9004,11 @@
           <t>narrateur|Avec rouge. Après le toboggan. Près de le chien. Nino s'arrête. Une tasse cliquette. Nino tend rouge à papa. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9098,6 +9176,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9265,6 +9344,11 @@
           <t>narrateur|Nino range le toboggan. bleu reste près de le chien. Un ruban reste dans la poche. Nino dit merci à maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9432,6 +9516,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9599,6 +9684,11 @@
           <t>narrateur|Vert est là. le toboggan aussi. le chien reste dans le souvenir. Le sol est un peu froid. Nino enfile ses chaussons. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9766,6 +9856,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9933,6 +10024,11 @@
           <t>narrateur|Nino va vers les balançoires. Il répète la règle. Un camarade observe d'abord. L'image du chien bouge un peu. Maman montre le geste, lentement. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10128,6 +10224,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10295,6 +10392,11 @@
           <t>narrateur|Nino rejoint rouge. les balançoires est rangé. le chien est fini. On se tient la main. Nino plie un pull. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10462,6 +10564,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10629,6 +10732,11 @@
           <t>narrateur|Près de bleu. Nino pose les balançoires. le chien est derrière. Le vent est doux. Nino caresse le doudou. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10796,6 +10904,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10963,6 +11072,11 @@
           <t>narrateur|Nino montre vert. Maman a vu le chien. Et les balançoires. On dit merci. Nino pose sa tête un moment. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11130,6 +11244,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11297,6 +11412,7 @@
           <t>narrateur|À l'école, on parle de la poule de la ferme. Un camarade n'entre pas tout de suite. Nino répète la règle. On peut observer d'abord. Papa arrivera plus tard. On attend. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11480,6 +11596,7 @@
           <t>narrateur|On force, ou on répète ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11651,6 +11768,7 @@
           <t>narrateur|Oui. On peut répéter. On peut observer d'abord. Nino hoche la tête. On continue, avec maman. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11842,6 +11960,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12009,6 +12128,7 @@
           <t>narrateur|Nino va vers le bac à sable. Il répète la règle. Un camarade observe d'abord. On parle de la poule, tout doux. Maman reste tout près. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12204,6 +12324,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12371,6 +12492,7 @@
           <t>narrateur|Nino a choisi la poule. Puis le bac à sable. Puis rouge. Les chaussures font toc toc. Nino prend la main de maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12538,6 +12660,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12705,6 +12828,7 @@
           <t>narrateur|Nino s'arrête près de bleu. le bac à sable est rangé. Une pomme brille un peu. Nino sourit. Maman sourit aussi. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12872,6 +12996,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13039,6 +13164,7 @@
           <t>narrateur|Nino se souvient de la poule. Et de le bac à sable. Et de vert. Un vélo passe au loin. Nino répète tout bas le geste. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13206,6 +13332,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13373,6 +13500,7 @@
           <t>narrateur|Nino va vers le toboggan. Il répète la règle. Un camarade observe d'abord. On parle de la poule, tout doux. Maman montre le geste, lentement. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13568,6 +13696,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13735,6 +13864,7 @@
           <t>narrateur|Avec rouge. Après le toboggan. Près de la poule. Nino s'arrête. Il y a des miettes sur la table. Nino raccroche un linge. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13902,6 +14032,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14069,6 +14200,7 @@
           <t>narrateur|Nino range le toboggan. bleu reste près de la poule. Le savon sent bon. Nino montre bleu à maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14236,6 +14368,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14403,6 +14536,7 @@
           <t>narrateur|Vert est là. le toboggan aussi. la poule reste dans le souvenir. On rit un peu. Nino boit une gorgée d'eau. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14570,6 +14704,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14738,6 +14873,7 @@
 maman|Je suis là. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14933,6 +15069,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15100,6 +15237,7 @@
           <t>narrateur|Nino rejoint rouge. les balançoires est rangé. la poule est fini. Une cloche tinte, tout loin. Nino serre la main de maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15267,6 +15405,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15436,6 +15575,7 @@
 narrateur|Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15603,6 +15743,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15770,6 +15911,7 @@
           <t>narrateur|Nino montre vert. Maman a vu la poule. Et les balançoires. Ça sent le pain chaud. Nino ferme la porte, tout doux. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15937,6 +16079,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15955,7 +16098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16035,6 +16178,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16049,7 +16206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16236,6 +16393,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-007.xlsx
+++ b/stories/arbres/TREE-DIF-007.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Plus de temps ou de calme — à l'école</t>
+          <t>Le rayon sur le casier</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un rayon touche le casier. Nino accroche son manteau. Un camarade a besoin de calme. Nino répète la règle. On laisse observer d'abord.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nino est à l'école, avec maman. Papa viendra plus tard. Un camarade a besoin de calme. Il regarde d'abord. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>Un rayon glisse sur le casier. Il touche un bouton de manteau. Le couloir sent le savon, et la banane. Une gouttière cliquette, tout dehors. La vitre a des gouttes, en file. Papa trace une goutte du doigt. Tu as vu le rayon, Nino ? Il est tout chaud. Le bouton brille, hein ? Oui, papa. Un bateau en papier attend sur le rebord. La craie a laissé un petit nuage. Les crochets font un clic, tout doux. On accroche le manteau, d'accord ? D'accord, maman. En ce moment, Nino pose son cartable. Le cartable est encore un peu froid. Un camarade reste près du mur. Il a besoin de calme. Il a besoin de plus de temps. Il regarde d'abord, sans bouger. On peut répéter la règle. On peut observer d'abord. Il ne vient pas encore. C'est possible. On attend. On répète la règle, tout doux. On laisse observer d'abord. Nino hoche la tête. On répète. On attend. Bravo, Nino. C'est du bon travail. Le coin du chat attend. Le coin du chien attend. Le coin de la poule attend. Tu es prêt ? Oui, maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,8 +1337,42 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Nino est à l'école, avec maman. Papa viendra plus tard. Un camarade a besoin de calme. Il regarde d'abord.
-maman|On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>narrateur|Un rayon glisse sur le casier.
+narrateur|Il touche un bouton de manteau.
+narrateur|Le couloir sent le savon, et la banane.
+narrateur|Une gouttière cliquette, tout dehors.
+narrateur|La vitre a des gouttes, en file.
+narrateur|Papa trace une goutte du doigt.
+maman|Tu as vu le rayon, Nino ?
+enfant-m|Il est tout chaud.
+papa|Le bouton brille, hein ?
+enfant-m|Oui, papa.
+narrateur|Un bateau en papier attend sur le rebord.
+narrateur|La craie a laissé un petit nuage.
+narrateur|Les crochets font un clic, tout doux.
+maman|On accroche le manteau, d'accord ?
+enfant-m|D'accord, maman.
+narrateur|En ce moment, Nino pose son cartable.
+narrateur|Le cartable est encore un peu froid.
+narrateur|Un camarade reste près du mur.
+narrateur|Il a besoin de calme.
+narrateur|Il a besoin de plus de temps.
+narrateur|Il regarde d'abord, sans bouger.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|Il ne vient pas encore.
+maman|C'est possible. On attend.
+papa|On répète la règle, tout doux.
+maman|On laisse observer d'abord.
+narrateur|Nino hoche la tête.
+enfant-m|On répète. On attend.
+papa|Bravo, Nino.
+maman|C'est du bon travail.
+narrateur|Le coin du chat attend.
+narrateur|Le coin du chien attend.
+narrateur|Le coin de la poule attend.
+maman|Tu es prêt ?
+enfant-m|Oui, maman.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1354,7 +1400,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>Nino va vers quel coin ? Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1518,7 +1564,8 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|Nino va vers quel coin ?
+maman|Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1550,7 +1597,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>À l'école, il y a un coin chat. Un camarade reste au bord. Nino répète la règle : on touche tout doux. On peut observer d'abord. Le camarade regarde. C'est bien. On peut jouer ensemble.</t>
+          <t>Nino va vers le coin du chat. Le chat en peluche est tout doux. Un camarade reste au bord. Il observe d'abord. On touche tout doux. Oui. Tu répètes la règle. On peut observer d'abord. Le camarade regarde. Il ne joue pas encore. C'est bien. On attend. On répète. On observe d'abord. Bravo, Nino. On peut jouer ensemble, plus tard. Le chat en peluche reste au calme.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1690,8 +1737,19 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|À l'école, il y a un coin chat. Un camarade reste au bord. Nino répète la règle : on touche tout doux. On peut observer d'abord. Le camarade regarde.
-maman|C'est bien. On peut jouer ensemble.</t>
+          <t>narrateur|Nino va vers le coin du chat.
+narrateur|Le chat en peluche est tout doux.
+narrateur|Un camarade reste au bord.
+narrateur|Il observe d'abord.
+enfant-m|On touche tout doux.
+maman|Oui. Tu répètes la règle.
+papa|On peut observer d'abord.
+narrateur|Le camarade regarde. Il ne joue pas encore.
+maman|C'est bien. On attend.
+enfant-m|On répète. On observe d'abord.
+papa|Bravo, Nino.
+maman|On peut jouer ensemble, plus tard.
+narrateur|Le chat en peluche reste au calme.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1903,7 +1961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. On peut répéter. On peut observer d'abord. Nino respire. Maman est là. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>Oui. On peut répéter la règle. On peut observer d'abord. Nino respire, tout calme. Bravo, Nino. Tu as fait du bon travail. Merci, maman. On continue, tout doux.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2047,7 +2105,14 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On peut répéter. On peut observer d'abord. Nino respire. Maman est là. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>narrateur|Oui.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+narrateur|Nino respire, tout calme.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+maman|On continue, tout doux.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2075,7 +2140,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>On joue où, dans la cour ? Le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2239,7 +2304,8 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>narrateur|On joue où, dans la cour ?
+papa|Le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2267,7 +2333,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Nino va vers le bac à sable. Il répète la règle : on reste assis. Un camarade observe d'abord. Le chat en peluche est là. Maman montre le geste, lentement. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>Nino va vers le bac à sable, après le chat. Le sable est frais, un peu rêche. Un camarade observe d'abord. On reste assis. On attend. Oui. Tu répètes la règle. On peut observer d'abord. Le camarade regarde le sable, de loin. C'est bien. On laisse le temps. On répète. On attend. Bravo, Nino. On peut jouer ensemble, plus tard. Un seau attend dans le sable.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2407,7 +2473,18 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Nino va vers le bac à sable. Il répète la règle : on reste assis. Un camarade observe d'abord. Le chat en peluche est là. Maman montre le geste, lentement. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>narrateur|Nino va vers le bac à sable, après le chat.
+narrateur|Le sable est frais, un peu rêche.
+narrateur|Un camarade observe d'abord.
+enfant-m|On reste assis. On attend.
+maman|Oui. Tu répètes la règle.
+papa|On peut observer d'abord.
+narrateur|Le camarade regarde le sable, de loin.
+maman|C'est bien. On laisse le temps.
+enfant-m|On répète. On attend.
+papa|Bravo, Nino.
+maman|On peut jouer ensemble, plus tard.
+narrateur|Un seau attend dans le sable.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2435,7 +2512,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>On prend quelle couleur ? Le rouge, le bleu, ou le vert.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2603,7 +2680,8 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|On prend quelle couleur ?
+maman|Le rouge, le bleu, ou le vert.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2631,7 +2709,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Nino a choisi le chat. Puis le bac à sable. Puis rouge. Un chat miaule une fois. Nino range la tasse. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Un seau rouge attend dans le sable. Le chat en peluche a un grain de sable. Nino a choisi le chat. Puis le bac à sable. Puis rouge. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient du chat, et du bac à sable.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2771,7 +2849,20 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Nino a choisi le chat. Puis le bac à sable. Puis rouge. Un chat miaule une fois. Nino range la tasse. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>narrateur|Un seau rouge attend dans le sable.
+narrateur|Le chat en peluche a un grain de sable.
+narrateur|Nino a choisi le chat.
+narrateur|Puis le bac à sable. Puis rouge.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient du chat, et du bac à sable.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2799,7 +2890,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin du chat. Il a joué à le bac à sable. Il a pris le rouge. Un grain de sable brille sur le seau rouge. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2939,7 +3030,15 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin du chat.
+narrateur|Il a joué à le bac à sable.
+narrateur|Il a pris le rouge.
+narrateur|Un grain de sable brille sur le seau rouge.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2967,7 +3066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Nino s'arrête près de bleu. le bac à sable est rangé. Un panier est posé sur le banc. Nino souffle, puis sourit à maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Un ruban bleu flotte près du bac. Le chat en peluche regarde le sable. Nino a choisi le chat. Puis le bac à sable. Puis bleu. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient du chat, et du bac à sable.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3107,7 +3206,20 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Nino s'arrête près de bleu. le bac à sable est rangé. Un panier est posé sur le banc. Nino souffle, puis sourit à maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>narrateur|Un ruban bleu flotte près du bac.
+narrateur|Le chat en peluche regarde le sable.
+narrateur|Nino a choisi le chat.
+narrateur|Puis le bac à sable. Puis bleu.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient du chat, et du bac à sable.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3135,7 +3247,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin du chat. Il a joué à le bac à sable. Il a pris le bleu. Le ruban bleu a pris un peu de vent. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3275,7 +3387,15 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin du chat.
+narrateur|Il a joué à le bac à sable.
+narrateur|Il a pris le bleu.
+narrateur|Le ruban bleu a pris un peu de vent.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3303,7 +3423,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Nino se souvient de le chat. Et de le bac à sable. Et de vert. L'eau coule, tout petit bruit. Nino essuie ses mains. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Une feuille verte colle au seau. Le chat en peluche reste au bord. Nino a choisi le chat. Puis le bac à sable. Puis vert. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient du chat, et du bac à sable.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3443,7 +3563,20 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Nino se souvient de le chat. Et de le bac à sable. Et de vert. L'eau coule, tout petit bruit. Nino essuie ses mains. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>narrateur|Une feuille verte colle au seau.
+narrateur|Le chat en peluche reste au bord.
+narrateur|Nino a choisi le chat.
+narrateur|Puis le bac à sable. Puis vert.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient du chat, et du bac à sable.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3471,7 +3604,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin du chat. Il a joué à le bac à sable. Il a pris le vert. La feuille verte a séché sur le seau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3611,7 +3744,15 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin du chat.
+narrateur|Il a joué à le bac à sable.
+narrateur|Il a pris le vert.
+narrateur|La feuille verte a séché sur le seau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3639,7 +3780,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Nino va vers le toboggan. Il répète la règle : un à la fois. Un camarade observe d'abord. Le chat en peluche attend. Je suis là. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>Nino va vers le toboggan, après le chat. Le plastique est froid, tout lisse. Un camarade observe d'abord. Un à la fois. On attend. Oui. Tu répètes la règle. On peut observer d'abord. Le camarade reste en bas, tout calme. C'est bien. On laisse regarder. On répète. On attend. Bravo. Tu as répété. On peut jouer ensemble, plus tard. Une feuille colle encore au toboggan.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3779,8 +3920,18 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Nino va vers le toboggan. Il répète la règle : un à la fois. Un camarade observe d'abord. Le chat en peluche attend.
-maman|Je suis là. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>narrateur|Nino va vers le toboggan, après le chat.
+narrateur|Le plastique est froid, tout lisse.
+narrateur|Un camarade observe d'abord.
+enfant-m|Un à la fois. On attend.
+papa|Oui. Tu répètes la règle.
+maman|On peut observer d'abord.
+narrateur|Le camarade reste en bas, tout calme.
+papa|C'est bien. On laisse regarder.
+enfant-m|On répète. On attend.
+maman|Bravo. Tu as répété.
+papa|On peut jouer ensemble, plus tard.
+narrateur|Une feuille colle encore au toboggan.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3808,7 +3959,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>On prend quelle couleur ? Le rouge, le bleu, ou le vert.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3976,7 +4127,8 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|On prend quelle couleur ?
+maman|Le rouge, le bleu, ou le vert.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -4004,7 +4156,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Avec rouge. Après le toboggan. Près de le chat. Nino s'arrête. Un linge sèche à l'air. Nino range encore un peu, près de maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Une craie rouge marque le toboggan. Le chat en peluche attend en bas. Nino a choisi le chat. Puis le toboggan. Puis rouge. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient du chat, et du toboggan.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4144,7 +4296,20 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Avec rouge. Après le toboggan. Près de le chat. Nino s'arrête. Un linge sèche à l'air. Nino range encore un peu, près de maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>narrateur|Une craie rouge marque le toboggan.
+narrateur|Le chat en peluche attend en bas.
+narrateur|Nino a choisi le chat.
+narrateur|Puis le toboggan. Puis rouge.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient du chat, et du toboggan.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4172,7 +4337,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin du chat. Il a joué à le toboggan. Il a pris le rouge. La craie rouge a laissé un trait, tout court. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4312,7 +4477,15 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin du chat.
+narrateur|Il a joué à le toboggan.
+narrateur|Il a pris le rouge.
+narrateur|La craie rouge a laissé un trait, tout court.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4340,7 +4513,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Nino range le toboggan. bleu reste près de le chat. On écoute jusqu'au bout. Papa n'est pas loin. Nino les rejoint. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Un manteau bleu sèche près du toboggan. Le chat en peluche a un poil au vent. Nino a choisi le chat. Puis le toboggan. Puis bleu. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient du chat, et du toboggan.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4480,7 +4653,20 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Nino range le toboggan. bleu reste près de le chat. On écoute jusqu'au bout. Papa n'est pas loin. Nino les rejoint. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>narrateur|Un manteau bleu sèche près du toboggan.
+narrateur|Le chat en peluche a un poil au vent.
+narrateur|Nino a choisi le chat.
+narrateur|Puis le toboggan. Puis bleu.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient du chat, et du toboggan.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4508,7 +4694,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin du chat. Il a joué à le toboggan. Il a pris le bleu. Le manteau bleu a gardé une odeur de pluie. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4648,7 +4834,15 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin du chat.
+narrateur|Il a joué à le toboggan.
+narrateur|Il a pris le bleu.
+narrateur|Le manteau bleu a gardé une odeur de pluie.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4676,7 +4870,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Vert est là. le toboggan aussi. le chat reste dans le souvenir. Une feuille tombe. Nino chuchote : c'est fini. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Un seau vert repose au pied du toboggan. Le chat en peluche observe, tout calme. Nino a choisi le chat. Puis le toboggan. Puis vert. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient du chat, et du toboggan.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4816,7 +5010,20 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Vert est là. le toboggan aussi. le chat reste dans le souvenir. Une feuille tombe. Nino chuchote : c'est fini. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>narrateur|Un seau vert repose au pied du toboggan.
+narrateur|Le chat en peluche observe, tout calme.
+narrateur|Nino a choisi le chat.
+narrateur|Puis le toboggan. Puis vert.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient du chat, et du toboggan.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4844,7 +5051,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin du chat. Il a joué à le toboggan. Il a pris le vert. Le seau vert a sonné, puis s'est tu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4984,7 +5191,15 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin du chat.
+narrateur|Il a joué à le toboggan.
+narrateur|Il a pris le vert.
+narrateur|Le seau vert a sonné, puis s'est tu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5012,7 +5227,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Nino va vers les balançoires. Il répète la règle : on s'arrête. Un camarade observe d'abord. Le chat en peluche est sur le banc. Maman reste tout près. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>Nino va vers les balançoires, après le chat. Une chaîne fait un petit clic. Un camarade observe d'abord. On s'arrête. On attend. Oui. Tu répètes la règle. On peut observer d'abord. Le camarade reste au bord, les mains dans les poches. C'est possible. On attend. On répète. On laisse regarder. Bravo, Nino. On peut jouer ensemble, plus tard. La balançoire vide bouge, tout léger.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5152,7 +5367,18 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Nino va vers les balançoires. Il répète la règle : on s'arrête. Un camarade observe d'abord. Le chat en peluche est sur le banc. Maman reste tout près. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>narrateur|Nino va vers les balançoires, après le chat.
+narrateur|Une chaîne fait un petit clic.
+narrateur|Un camarade observe d'abord.
+enfant-m|On s'arrête. On attend.
+maman|Oui. Tu répètes la règle.
+papa|On peut observer d'abord.
+narrateur|Le camarade reste au bord, les mains dans les poches.
+maman|C'est possible. On attend.
+enfant-m|On répète. On laisse regarder.
+papa|Bravo, Nino.
+maman|On peut jouer ensemble, plus tard.
+narrateur|La balançoire vide bouge, tout léger.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5180,7 +5406,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>On prend quelle couleur ? Le rouge, le bleu, ou le vert.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5348,7 +5574,8 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|On prend quelle couleur ?
+maman|Le rouge, le bleu, ou le vert.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5376,7 +5603,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Nino rejoint rouge. les balançoires est rangé. le chat est fini. La lumière est claire. Nino s'assoit près de maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Un ruban rouge noue la balançoire. Le chat en peluche est sur le banc. Nino a choisi le chat. Puis les balançoires. Puis rouge. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient du chat, et des balançoires.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5516,7 +5743,20 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Nino rejoint rouge. les balançoires est rangé. le chat est fini. La lumière est claire. Nino s'assoit près de maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>narrateur|Un ruban rouge noue la balançoire.
+narrateur|Le chat en peluche est sur le banc.
+narrateur|Nino a choisi le chat.
+narrateur|Puis les balançoires. Puis rouge.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient du chat, et des balançoires.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5544,7 +5784,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin du chat. Il a joué à les balançoires. Il a pris le rouge. Le ruban rouge a bougé, tout léger. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5684,7 +5924,15 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin du chat.
+narrateur|Il a joué à les balançoires.
+narrateur|Il a pris le rouge.
+narrateur|Le ruban rouge a bougé, tout léger.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5712,7 +5960,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Près de bleu. Nino pose les balançoires. le chat est derrière. On attend son tour. Nino pose les balançoires à sa place. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Un seau bleu attend sous la balançoire. Le chat en peluche a fermé un œil. Nino a choisi le chat. Puis les balançoires. Puis bleu. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient du chat, et des balançoires.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5852,7 +6100,20 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Près de bleu. Nino pose les balançoires. le chat est derrière. On attend son tour. Nino pose les balançoires à sa place. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>narrateur|Un seau bleu attend sous la balançoire.
+narrateur|Le chat en peluche a fermé un œil.
+narrateur|Nino a choisi le chat.
+narrateur|Puis les balançoires. Puis bleu.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient du chat, et des balançoires.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5880,7 +6141,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin du chat. Il a joué à les balançoires. Il a pris le bleu. Le seau bleu a gardé une goutte. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6020,7 +6281,15 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin du chat.
+narrateur|Il a joué à les balançoires.
+narrateur|Il a pris le bleu.
+narrateur|Le seau bleu a gardé une goutte.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6048,7 +6317,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Nino montre vert. Maman a vu le chat. Et les balançoires. Un ballon s'immobilise. Nino ferme le sac. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Une craie verte trace un trait au sol. Le chat en peluche reste près de Nino. Nino a choisi le chat. Puis les balançoires. Puis vert. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient du chat, et des balançoires.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6188,7 +6457,20 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Nino montre vert. Maman a vu le chat. Et les balançoires. Un ballon s'immobilise. Nino ferme le sac. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>narrateur|Une craie verte trace un trait au sol.
+narrateur|Le chat en peluche reste près de Nino.
+narrateur|Nino a choisi le chat.
+narrateur|Puis les balançoires. Puis vert.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient du chat, et des balançoires.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6216,7 +6498,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin du chat. Il a joué à les balançoires. Il a pris le vert. Le trait vert est encore sur le sol. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6356,7 +6638,15 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin du chat.
+narrateur|Il a joué à les balançoires.
+narrateur|Il a pris le vert.
+narrateur|Le trait vert est encore sur le sol.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6384,7 +6674,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>À l'école, il y a un coin chien en images. Un camarade a besoin de calme. Nino répète la règle. On peut observer d'abord. Le camarade respire. Puis il s'approche. On peut jouer ensemble.</t>
+          <t>Nino va vers le coin du chien. Une image de chien est sur le mur. Un camarade a besoin de calme. Il reste près du mur. On parle tout doux. Oui. Tu répètes la règle. On peut observer d'abord. Le camarade écoute. Il regarde l'image. C'est bien. On laisse le temps. On répète. On attend. Bravo. Tu as répété. On peut jouer ensemble, plus tard. L'image du chien reste, tout calme.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6524,7 +6814,19 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|À l'école, il y a un coin chien en images. Un camarade a besoin de calme. Nino répète la règle. On peut observer d'abord. Le camarade respire. Puis il s'approche. On peut jouer ensemble.</t>
+          <t>narrateur|Nino va vers le coin du chien.
+narrateur|Une image de chien est sur le mur.
+narrateur|Un camarade a besoin de calme.
+narrateur|Il reste près du mur.
+enfant-m|On parle tout doux.
+papa|Oui. Tu répètes la règle.
+maman|On peut observer d'abord.
+narrateur|Le camarade écoute. Il regarde l'image.
+papa|C'est bien. On laisse le temps.
+enfant-m|On répète. On attend.
+maman|Bravo. Tu as répété.
+papa|On peut jouer ensemble, plus tard.
+narrateur|L'image du chien reste, tout calme.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -6744,7 +7046,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. On peut répéter. On peut observer d'abord. Nino retient le geste. Maman sourit. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>Oui. On peut observer d'abord. On peut répéter la règle. Nino retient le geste. Bravo. Tu as laissé le temps. Il observe d'abord. Oui. C'est ça.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6888,7 +7190,14 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On peut répéter. On peut observer d'abord. Nino retient le geste. Maman sourit. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>narrateur|Oui.
+papa|On peut observer d'abord.
+maman|On peut répéter la règle.
+narrateur|Nino retient le geste.
+papa|Bravo.
+papa|Tu as laissé le temps.
+enfant-m|Il observe d'abord.
+maman|Oui. C'est ça.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6916,7 +7225,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>On joue où, dans la cour ? Le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7080,7 +7389,8 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>narrateur|On joue où, dans la cour ?
+papa|Le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7108,7 +7418,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Nino va vers le bac à sable. Il répète la règle. Un camarade observe d'abord. L'image du chien est collée au seau. Je suis là. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>Nino va vers le bac à sable, après le chien. Le sable est frais, un peu rêche. Un camarade observe d'abord. On reste assis. On attend. Oui. Tu répètes la règle. On peut observer d'abord. Le camarade regarde le sable, de loin. C'est bien. On laisse le temps. On répète. On attend. Bravo, Nino. On peut jouer ensemble, plus tard. Un seau attend dans le sable.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7248,8 +7558,18 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Nino va vers le bac à sable. Il répète la règle. Un camarade observe d'abord. L'image du chien est collée au seau.
-maman|Je suis là. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>narrateur|Nino va vers le bac à sable, après le chien.
+narrateur|Le sable est frais, un peu rêche.
+narrateur|Un camarade observe d'abord.
+enfant-m|On reste assis. On attend.
+maman|Oui. Tu répètes la règle.
+papa|On peut observer d'abord.
+narrateur|Le camarade regarde le sable, de loin.
+maman|C'est bien. On laisse le temps.
+enfant-m|On répète. On attend.
+papa|Bravo, Nino.
+maman|On peut jouer ensemble, plus tard.
+narrateur|Un seau attend dans le sable.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -7281,7 +7601,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>On prend quelle couleur ? Le rouge, le bleu, ou le vert.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7449,7 +7769,8 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|On prend quelle couleur ?
+maman|Le rouge, le bleu, ou le vert.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7477,7 +7798,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Nino a choisi le chien. Puis le bac à sable. Puis rouge. Une chaussette est encore sablée. Nino écoute maman encore une fois. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Un seau rouge sonne dans le sable. L'image du chien est encore dans la tête. Nino a choisi le chien. Puis le bac à sable. Puis rouge. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient du chien, et du bac à sable.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7617,7 +7938,20 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Nino a choisi le chien. Puis le bac à sable. Puis rouge. Une chaussette est encore sablée. Nino écoute maman encore une fois. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>narrateur|Un seau rouge sonne dans le sable.
+narrateur|L'image du chien est encore dans la tête.
+narrateur|Nino a choisi le chien.
+narrateur|Puis le bac à sable. Puis rouge.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient du chien, et du bac à sable.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -7649,7 +7983,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin du chien. Il a joué à le bac à sable. Il a pris le rouge. Le seau rouge a un cercle de sable. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7789,7 +8123,15 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin du chien.
+narrateur|Il a joué à le bac à sable.
+narrateur|Il a pris le rouge.
+narrateur|Le seau rouge a un cercle de sable.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7817,7 +8159,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Nino s'arrête près de bleu. le bac à sable est rangé. On souffle doucement. Nino marche près de maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Un galet bleu brille dans le bac. Le chien de l'image a l'air calme. Nino a choisi le chien. Puis le bac à sable. Puis bleu. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient du chien, et du bac à sable.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7957,10 +8299,27 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Nino s'arrête près de bleu. le bac à sable est rangé. On souffle doucement. Nino marche près de maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr"/>
+          <t>narrateur|Un galet bleu brille dans le bac.
+narrateur|Le chien de l'image a l'air calme.
+narrateur|Nino a choisi le chien.
+narrateur|Puis le bac à sable. Puis bleu.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient du chien, et du bac à sable.</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7985,7 +8344,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin du chien. Il a joué à le bac à sable. Il a pris le bleu. Le galet bleu est froid, tout lisse. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8125,7 +8484,15 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin du chien.
+narrateur|Il a joué à le bac à sable.
+narrateur|Il a pris le bleu.
+narrateur|Le galet bleu est froid, tout lisse.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8153,7 +8520,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Nino se souvient de le chien. Et de le bac à sable. Et de vert. Un galet est encore chaud. Nino range le chien dans sa tête, comme un souvenir. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Une pelle verte repose dans le sable. Le camarade regarde encore le chien. Nino a choisi le chien. Puis le bac à sable. Puis vert. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient du chien, et du bac à sable.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8293,7 +8660,20 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Nino se souvient de le chien. Et de le bac à sable. Et de vert. Un galet est encore chaud. Nino range le chien dans sa tête, comme un souvenir. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>narrateur|Une pelle verte repose dans le sable.
+narrateur|Le camarade regarde encore le chien.
+narrateur|Nino a choisi le chien.
+narrateur|Puis le bac à sable. Puis vert.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient du chien, et du bac à sable.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -8325,7 +8705,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin du chien. Il a joué à le bac à sable. Il a pris le vert. La pelle verte a une trace de main. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8465,7 +8845,15 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin du chien.
+narrateur|Il a joué à le bac à sable.
+narrateur|Il a pris le vert.
+narrateur|La pelle verte a une trace de main.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8493,7 +8881,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Nino va vers le toboggan. Il répète la règle. Un camarade observe d'abord. L'image du chien est sur la rampe. Maman reste tout près. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>Nino va vers le toboggan, après le chien. Le plastique est froid, tout lisse. Un camarade observe d'abord. Un à la fois. On attend. Oui. Tu répètes la règle. On peut observer d'abord. Le camarade reste en bas, tout calme. C'est bien. On laisse regarder. On répète. On attend. Bravo. Tu as répété. On peut jouer ensemble, plus tard. Une feuille colle encore au toboggan.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8633,7 +9021,18 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Nino va vers le toboggan. Il répète la règle. Un camarade observe d'abord. L'image du chien est sur la rampe. Maman reste tout près. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>narrateur|Nino va vers le toboggan, après le chien.
+narrateur|Le plastique est froid, tout lisse.
+narrateur|Un camarade observe d'abord.
+enfant-m|Un à la fois. On attend.
+papa|Oui. Tu répètes la règle.
+maman|On peut observer d'abord.
+narrateur|Le camarade reste en bas, tout calme.
+papa|C'est bien. On laisse regarder.
+enfant-m|On répète. On attend.
+maman|Bravo. Tu as répété.
+papa|On peut jouer ensemble, plus tard.
+narrateur|Une feuille colle encore au toboggan.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -8665,7 +9064,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>On prend quelle couleur ? Le rouge, le bleu, ou le vert.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8833,7 +9232,8 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|On prend quelle couleur ?
+maman|Le rouge, le bleu, ou le vert.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8861,7 +9261,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Avec rouge. Après le toboggan. Près de le chien. Nino s'arrête. Une tasse cliquette. Nino tend rouge à papa. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Une balle rouge attend près du toboggan. L'image du chien reste au mur, tout loin. Nino a choisi le chien. Puis le toboggan. Puis rouge. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient du chien, et du toboggan.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -9001,7 +9401,20 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Avec rouge. Après le toboggan. Près de le chien. Nino s'arrête. Une tasse cliquette. Nino tend rouge à papa. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>narrateur|Une balle rouge attend près du toboggan.
+narrateur|L'image du chien reste au mur, tout loin.
+narrateur|Nino a choisi le chien.
+narrateur|Puis le toboggan. Puis rouge.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient du chien, et du toboggan.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
@@ -9033,7 +9446,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin du chien. Il a joué à le toboggan. Il a pris le rouge. La balle rouge s'est arrêtée, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9173,7 +9586,15 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin du chien.
+narrateur|Il a joué à le toboggan.
+narrateur|Il a pris le rouge.
+narrateur|La balle rouge s'est arrêtée, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9201,7 +9622,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Nino range le toboggan. bleu reste près de le chien. Un ruban reste dans la poche. Nino dit merci à maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Un ruban bleu claque au vent. Le toboggan est froid, comme le calme. Nino a choisi le chien. Puis le toboggan. Puis bleu. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient du chien, et du toboggan.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9341,7 +9762,20 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Nino range le toboggan. bleu reste près de le chien. Un ruban reste dans la poche. Nino dit merci à maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>narrateur|Un ruban bleu claque au vent.
+narrateur|Le toboggan est froid, comme le calme.
+narrateur|Nino a choisi le chien.
+narrateur|Puis le toboggan. Puis bleu.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient du chien, et du toboggan.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -9373,7 +9807,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin du chien. Il a joué à le toboggan. Il a pris le bleu. Le ruban bleu s'est endormi au vent. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9513,7 +9947,15 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin du chien.
+narrateur|Il a joué à le toboggan.
+narrateur|Il a pris le bleu.
+narrateur|Le ruban bleu s'est endormi au vent.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9541,7 +9983,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Vert est là. le toboggan aussi. le chien reste dans le souvenir. Le sol est un peu froid. Nino enfile ses chaussons. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Une feuille verte colle à la rampe. Le camarade observe le chien, puis le jeu. Nino a choisi le chien. Puis le toboggan. Puis vert. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient du chien, et du toboggan.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9681,7 +10123,20 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Vert est là. le toboggan aussi. le chien reste dans le souvenir. Le sol est un peu froid. Nino enfile ses chaussons. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>narrateur|Une feuille verte colle à la rampe.
+narrateur|Le camarade observe le chien, puis le jeu.
+narrateur|Nino a choisi le chien.
+narrateur|Puis le toboggan. Puis vert.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient du chien, et du toboggan.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
@@ -9713,7 +10168,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin du chien. Il a joué à le toboggan. Il a pris le vert. La feuille verte reste collée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9853,7 +10308,15 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin du chien.
+narrateur|Il a joué à le toboggan.
+narrateur|Il a pris le vert.
+narrateur|La feuille verte reste collée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9881,7 +10344,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Nino va vers les balançoires. Il répète la règle. Un camarade observe d'abord. L'image du chien bouge un peu. Maman montre le geste, lentement. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>Nino va vers les balançoires, après le chien. Une chaîne fait un petit clic. Un camarade observe d'abord. On s'arrête. On attend. Oui. Tu répètes la règle. On peut observer d'abord. Le camarade reste au bord, les mains dans les poches. C'est possible. On attend. On répète. On laisse regarder. Bravo, Nino. On peut jouer ensemble, plus tard. La balançoire vide bouge, tout léger.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -10021,7 +10484,18 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Nino va vers les balançoires. Il répète la règle. Un camarade observe d'abord. L'image du chien bouge un peu. Maman montre le geste, lentement. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>narrateur|Nino va vers les balançoires, après le chien.
+narrateur|Une chaîne fait un petit clic.
+narrateur|Un camarade observe d'abord.
+enfant-m|On s'arrête. On attend.
+maman|Oui. Tu répètes la règle.
+papa|On peut observer d'abord.
+narrateur|Le camarade reste au bord, les mains dans les poches.
+maman|C'est possible. On attend.
+enfant-m|On répète. On laisse regarder.
+papa|Bravo, Nino.
+maman|On peut jouer ensemble, plus tard.
+narrateur|La balançoire vide bouge, tout léger.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
@@ -10053,7 +10527,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>On prend quelle couleur ? Le rouge, le bleu, ou le vert.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10221,7 +10695,8 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|On prend quelle couleur ?
+maman|Le rouge, le bleu, ou le vert.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10249,7 +10724,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Nino rejoint rouge. les balançoires est rangé. le chien est fini. On se tient la main. Nino plie un pull. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Un manteau rouge pend près des balançoires. Le chien de l'image a une oreille pliée. Nino a choisi le chien. Puis les balançoires. Puis rouge. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient du chien, et des balançoires.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10389,7 +10864,20 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Nino rejoint rouge. les balançoires est rangé. le chien est fini. On se tient la main. Nino plie un pull. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>narrateur|Un manteau rouge pend près des balançoires.
+narrateur|Le chien de l'image a une oreille pliée.
+narrateur|Nino a choisi le chien.
+narrateur|Puis les balançoires. Puis rouge.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient du chien, et des balançoires.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
@@ -10421,7 +10909,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin du chien. Il a joué à les balançoires. Il a pris le rouge. Le manteau rouge a un bouton qui brille. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10561,7 +11049,15 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin du chien.
+narrateur|Il a joué à les balançoires.
+narrateur|Il a pris le rouge.
+narrateur|Le manteau rouge a un bouton qui brille.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10589,7 +11085,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Près de bleu. Nino pose les balançoires. le chien est derrière. Le vent est doux. Nino caresse le doudou. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Un seau bleu pose sur le banc. La chaîne des balançoires fait clic. Nino a choisi le chien. Puis les balançoires. Puis bleu. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient du chien, et des balançoires.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10729,7 +11225,20 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Près de bleu. Nino pose les balançoires. le chien est derrière. Le vent est doux. Nino caresse le doudou. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>narrateur|Un seau bleu pose sur le banc.
+narrateur|La chaîne des balançoires fait clic.
+narrateur|Nino a choisi le chien.
+narrateur|Puis les balançoires. Puis bleu.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient du chien, et des balançoires.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
@@ -10761,7 +11270,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin du chien. Il a joué à les balançoires. Il a pris le bleu. Le seau bleu a fait un dernier clic. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10901,7 +11410,15 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin du chien.
+narrateur|Il a joué à les balançoires.
+narrateur|Il a pris le bleu.
+narrateur|Le seau bleu a fait un dernier clic.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10929,7 +11446,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Nino montre vert. Maman a vu le chien. Et les balançoires. On dit merci. Nino pose sa tête un moment. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Un galet vert est sous la balançoire. Le camarade a encore besoin de calme. Nino a choisi le chien. Puis les balançoires. Puis vert. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient du chien, et des balançoires.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11069,7 +11586,20 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Nino montre vert. Maman a vu le chien. Et les balançoires. On dit merci. Nino pose sa tête un moment. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>narrateur|Un galet vert est sous la balançoire.
+narrateur|Le camarade a encore besoin de calme.
+narrateur|Nino a choisi le chien.
+narrateur|Puis les balançoires. Puis vert.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient du chien, et des balançoires.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
@@ -11101,7 +11631,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin du chien. Il a joué à les balançoires. Il a pris le vert. Le galet vert a une tache d'eau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11241,7 +11771,15 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin du chien.
+narrateur|Il a joué à les balançoires.
+narrateur|Il a pris le vert.
+narrateur|Le galet vert a une tache d'eau.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11269,7 +11807,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>À l'école, on parle de la poule de la ferme. Un camarade n'entre pas tout de suite. Nino répète la règle. On peut observer d'abord. Papa arrivera plus tard. On attend. On peut jouer ensemble.</t>
+          <t>Nino va vers le coin de la poule. Une image de ferme est sur la table. Un camarade n'entre pas tout de suite. Il observe d'abord. On reste assis. On attend. Oui. Tu répètes la règle. On peut observer d'abord. Le camarade hoche la tête, de loin. C'est possible. On attend. On répète. On laisse regarder. Bravo, Nino. On peut jouer ensemble, plus tard. La poule de papier reste sur la table.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11409,7 +11947,19 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|À l'école, on parle de la poule de la ferme. Un camarade n'entre pas tout de suite. Nino répète la règle. On peut observer d'abord. Papa arrivera plus tard. On attend. On peut jouer ensemble.</t>
+          <t>narrateur|Nino va vers le coin de la poule.
+narrateur|Une image de ferme est sur la table.
+narrateur|Un camarade n'entre pas tout de suite.
+narrateur|Il observe d'abord.
+enfant-m|On reste assis. On attend.
+maman|Oui. Tu répètes la règle.
+papa|On peut observer d'abord.
+narrateur|Le camarade hoche la tête, de loin.
+maman|C'est possible. On attend.
+enfant-m|On répète. On laisse regarder.
+papa|Bravo, Nino.
+maman|On peut jouer ensemble, plus tard.
+narrateur|La poule de papier reste sur la table.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11437,7 +11987,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>On force, ou on répète ?</t>
+          <t>On répète, ou on attend ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11593,7 +12143,7 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|On force, ou on répète ?</t>
+          <t>narrateur|On répète, ou on attend ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11621,7 +12171,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. On peut répéter. On peut observer d'abord. Nino hoche la tête. On continue, avec maman. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>Oui. On répète. On attend. On laisse observer d'abord. Nino hoche la tête. Bravo, Nino. Tu as fait du bon travail. Merci, papa. On continue, tout doux.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11765,7 +12315,14 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On peut répéter. On peut observer d'abord. Nino hoche la tête. On continue, avec maman. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>narrateur|Oui.
+maman|On répète. On attend.
+papa|On laisse observer d'abord.
+narrateur|Nino hoche la tête.
+maman|Bravo, Nino.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+papa|On continue, tout doux.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11793,7 +12350,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>On joue où, dans la cour ? Le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11957,7 +12514,8 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>narrateur|On joue où, dans la cour ?
+papa|Le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11985,7 +12543,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Nino va vers le bac à sable. Il répète la règle. Un camarade observe d'abord. On parle de la poule, tout doux. Maman reste tout près. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>Nino va vers le bac à sable, après la poule. Le sable est frais, un peu rêche. Un camarade observe d'abord. On reste assis. On attend. Oui. Tu répètes la règle. On peut observer d'abord. Le camarade regarde le sable, de loin. C'est bien. On laisse le temps. On répète. On attend. Bravo, Nino. On peut jouer ensemble, plus tard. Un seau attend dans le sable.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12125,7 +12683,18 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Nino va vers le bac à sable. Il répète la règle. Un camarade observe d'abord. On parle de la poule, tout doux. Maman reste tout près. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>narrateur|Nino va vers le bac à sable, après la poule.
+narrateur|Le sable est frais, un peu rêche.
+narrateur|Un camarade observe d'abord.
+enfant-m|On reste assis. On attend.
+maman|Oui. Tu répètes la règle.
+papa|On peut observer d'abord.
+narrateur|Le camarade regarde le sable, de loin.
+maman|C'est bien. On laisse le temps.
+enfant-m|On répète. On attend.
+papa|Bravo, Nino.
+maman|On peut jouer ensemble, plus tard.
+narrateur|Un seau attend dans le sable.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr"/>
@@ -12153,7 +12722,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>On prend quelle couleur ? Le rouge, le bleu, ou le vert.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12321,7 +12890,8 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|On prend quelle couleur ?
+maman|Le rouge, le bleu, ou le vert.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12349,7 +12919,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Nino a choisi la poule. Puis le bac à sable. Puis rouge. Les chaussures font toc toc. Nino prend la main de maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Un seau rouge a un peu de sable. La poule de papier a une aile pliée. Nino a choisi la poule. Puis le bac à sable. Puis rouge. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient de la poule, et du bac à sable.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12489,7 +13059,20 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Nino a choisi la poule. Puis le bac à sable. Puis rouge. Les chaussures font toc toc. Nino prend la main de maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>narrateur|Un seau rouge a un peu de sable.
+narrateur|La poule de papier a une aile pliée.
+narrateur|Nino a choisi la poule.
+narrateur|Puis le bac à sable. Puis rouge.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient de la poule, et du bac à sable.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12517,7 +13100,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin de la poule. Il a joué à le bac à sable. Il a pris le rouge. Le seau rouge a gardé un peu de terre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12657,7 +13240,15 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin de la poule.
+narrateur|Il a joué à le bac à sable.
+narrateur|Il a pris le rouge.
+narrateur|Le seau rouge a gardé un peu de terre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12685,7 +13276,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Nino s'arrête près de bleu. le bac à sable est rangé. Une pomme brille un peu. Nino sourit. Maman sourit aussi. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Une craie bleue marque le bord du bac. La poule de papier regarde le sable. Nino a choisi la poule. Puis le bac à sable. Puis bleu. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient de la poule, et du bac à sable.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12825,7 +13416,20 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Nino s'arrête près de bleu. le bac à sable est rangé. Une pomme brille un peu. Nino sourit. Maman sourit aussi. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>narrateur|Une craie bleue marque le bord du bac.
+narrateur|La poule de papier regarde le sable.
+narrateur|Nino a choisi la poule.
+narrateur|Puis le bac à sable. Puis bleu.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient de la poule, et du bac à sable.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12853,7 +13457,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin de la poule. Il a joué à le bac à sable. Il a pris le bleu. La craie bleue s'est usée, tout petit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12993,7 +13597,15 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin de la poule.
+narrateur|Il a joué à le bac à sable.
+narrateur|Il a pris le bleu.
+narrateur|La craie bleue s'est usée, tout petit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -13021,7 +13633,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Nino se souvient de la poule. Et de le bac à sable. Et de vert. Un vélo passe au loin. Nino répète tout bas le geste. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Un brin d'herbe vert pique le seau. La poule de papier reste sur la table, tout loin. Nino a choisi la poule. Puis le bac à sable. Puis vert. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient de la poule, et du bac à sable.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13161,7 +13773,20 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Nino se souvient de la poule. Et de le bac à sable. Et de vert. Un vélo passe au loin. Nino répète tout bas le geste. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>narrateur|Un brin d'herbe vert pique le seau.
+narrateur|La poule de papier reste sur la table, tout loin.
+narrateur|Nino a choisi la poule.
+narrateur|Puis le bac à sable. Puis vert.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient de la poule, et du bac à sable.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13189,7 +13814,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin de la poule. Il a joué à le bac à sable. Il a pris le vert. Le brin d'herbe vert a plié, puis repris. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13329,7 +13954,15 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin de la poule.
+narrateur|Il a joué à le bac à sable.
+narrateur|Il a pris le vert.
+narrateur|Le brin d'herbe vert a plié, puis repris.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13357,7 +13990,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Nino va vers le toboggan. Il répète la règle. Un camarade observe d'abord. On parle de la poule, tout doux. Maman montre le geste, lentement. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>Nino va vers le toboggan, après la poule. Le plastique est froid, tout lisse. Un camarade observe d'abord. Un à la fois. On attend. Oui. Tu répètes la règle. On peut observer d'abord. Le camarade reste en bas, tout calme. C'est bien. On laisse regarder. On répète. On attend. Bravo. Tu as répété. On peut jouer ensemble, plus tard. Une feuille colle encore au toboggan.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13497,7 +14130,18 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Nino va vers le toboggan. Il répète la règle. Un camarade observe d'abord. On parle de la poule, tout doux. Maman montre le geste, lentement. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>narrateur|Nino va vers le toboggan, après la poule.
+narrateur|Le plastique est froid, tout lisse.
+narrateur|Un camarade observe d'abord.
+enfant-m|Un à la fois. On attend.
+papa|Oui. Tu répètes la règle.
+maman|On peut observer d'abord.
+narrateur|Le camarade reste en bas, tout calme.
+papa|C'est bien. On laisse regarder.
+enfant-m|On répète. On attend.
+maman|Bravo. Tu as répété.
+papa|On peut jouer ensemble, plus tard.
+narrateur|Une feuille colle encore au toboggan.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13525,7 +14169,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>On prend quelle couleur ? Le rouge, le bleu, ou le vert.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13693,7 +14337,8 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|On prend quelle couleur ?
+maman|Le rouge, le bleu, ou le vert.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13721,7 +14366,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Avec rouge. Après le toboggan. Près de la poule. Nino s'arrête. Il y a des miettes sur la table. Nino raccroche un linge. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Un gobelet rouge attend au toboggan. La poule de papier a un point d'œil. Nino a choisi la poule. Puis le toboggan. Puis rouge. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient de la poule, et du toboggan.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13861,7 +14506,20 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Avec rouge. Après le toboggan. Près de la poule. Nino s'arrête. Il y a des miettes sur la table. Nino raccroche un linge. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>narrateur|Un gobelet rouge attend au toboggan.
+narrateur|La poule de papier a un point d'œil.
+narrateur|Nino a choisi la poule.
+narrateur|Puis le toboggan. Puis rouge.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient de la poule, et du toboggan.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13889,7 +14547,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin de la poule. Il a joué à le toboggan. Il a pris le rouge. Le gobelet rouge a une goutte, au fond. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -14029,7 +14687,15 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin de la poule.
+narrateur|Il a joué à le toboggan.
+narrateur|Il a pris le rouge.
+narrateur|Le gobelet rouge a une goutte, au fond.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14057,7 +14723,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Nino range le toboggan. bleu reste près de la poule. Le savon sent bon. Nino montre bleu à maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Un manteau bleu fait un dos de toboggan. La poule de papier sent encore la colle. Nino a choisi la poule. Puis le toboggan. Puis bleu. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient de la poule, et du toboggan.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14197,7 +14863,20 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Nino range le toboggan. bleu reste près de la poule. Le savon sent bon. Nino montre bleu à maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>narrateur|Un manteau bleu fait un dos de toboggan.
+narrateur|La poule de papier sent encore la colle.
+narrateur|Nino a choisi la poule.
+narrateur|Puis le toboggan. Puis bleu.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient de la poule, et du toboggan.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14225,7 +14904,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin de la poule. Il a joué à le toboggan. Il a pris le bleu. Le manteau bleu a séché au soleil. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14365,7 +15044,15 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin de la poule.
+narrateur|Il a joué à le toboggan.
+narrateur|Il a pris le bleu.
+narrateur|Le manteau bleu a séché au soleil.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14393,7 +15080,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Vert est là. le toboggan aussi. la poule reste dans le souvenir. On rit un peu. Nino boit une gorgée d'eau. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Un seau vert sonne, tout creux. Le camarade observe la poule, puis le jeu. Nino a choisi la poule. Puis le toboggan. Puis vert. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient de la poule, et du toboggan.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14533,7 +15220,20 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Vert est là. le toboggan aussi. la poule reste dans le souvenir. On rit un peu. Nino boit une gorgée d'eau. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>narrateur|Un seau vert sonne, tout creux.
+narrateur|Le camarade observe la poule, puis le jeu.
+narrateur|Nino a choisi la poule.
+narrateur|Puis le toboggan. Puis vert.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient de la poule, et du toboggan.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14561,7 +15261,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin de la poule. Il a joué à le toboggan. Il a pris le vert. Le seau vert est rentré près du mur. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14701,7 +15401,15 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin de la poule.
+narrateur|Il a joué à le toboggan.
+narrateur|Il a pris le vert.
+narrateur|Le seau vert est rentré près du mur.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14729,7 +15437,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Nino va vers les balançoires. Il répète la règle. Un camarade observe d'abord. On parle de la poule, tout doux. Je suis là. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>Nino va vers les balançoires, après la poule. Une chaîne fait un petit clic. Un camarade observe d'abord. On s'arrête. On attend. Oui. Tu répètes la règle. On peut observer d'abord. Le camarade reste au bord, les mains dans les poches. C'est possible. On attend. On répète. On laisse regarder. Bravo, Nino. On peut jouer ensemble, plus tard. La balançoire vide bouge, tout léger.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14869,8 +15577,18 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Nino va vers les balançoires. Il répète la règle. Un camarade observe d'abord. On parle de la poule, tout doux.
-maman|Je suis là. On peut répéter la règle. On peut observer d'abord. On peut jouer ensemble.</t>
+          <t>narrateur|Nino va vers les balançoires, après la poule.
+narrateur|Une chaîne fait un petit clic.
+narrateur|Un camarade observe d'abord.
+enfant-m|On s'arrête. On attend.
+maman|Oui. Tu répètes la règle.
+papa|On peut observer d'abord.
+narrateur|Le camarade reste au bord, les mains dans les poches.
+maman|C'est possible. On attend.
+enfant-m|On répète. On laisse regarder.
+papa|Bravo, Nino.
+maman|On peut jouer ensemble, plus tard.
+narrateur|La balançoire vide bouge, tout léger.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14898,7 +15616,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>On prend quelle couleur ? Le rouge, le bleu, ou le vert.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15066,7 +15784,8 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|On prend quelle couleur ?
+maman|Le rouge, le bleu, ou le vert.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15094,7 +15813,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Nino rejoint rouge. les balançoires est rangé. la poule est fini. Une cloche tinte, tout loin. Nino serre la main de maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Un ruban rouge danse à la balançoire. La poule de papier a une plume peinte. Nino a choisi la poule. Puis les balançoires. Puis rouge. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient de la poule, et des balançoires.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15234,7 +15953,20 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Nino rejoint rouge. les balançoires est rangé. la poule est fini. Une cloche tinte, tout loin. Nino serre la main de maman. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>narrateur|Un ruban rouge danse à la balançoire.
+narrateur|La poule de papier a une plume peinte.
+narrateur|Nino a choisi la poule.
+narrateur|Puis les balançoires. Puis rouge.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient de la poule, et des balançoires.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15262,7 +15994,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin de la poule. Il a joué à les balançoires. Il a pris le rouge. Le ruban rouge s'est dénoué, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15402,7 +16134,15 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin de la poule.
+narrateur|Il a joué à les balançoires.
+narrateur|Il a pris le rouge.
+narrateur|Le ruban rouge s'est dénoué, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15430,7 +16170,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Près de bleu. Nino pose les balançoires. la poule est derrière. La couverture est douce. J'ai appris. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Un seau bleu est sous le banc. La poule de papier reste dans le souvenir. Nino a choisi la poule. Puis les balançoires. Puis bleu. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient de la poule, et des balançoires.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15570,9 +16310,20 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Près de bleu. Nino pose les balançoires. la poule est derrière. La couverture est douce.
-enfant-m|J'ai appris. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord.
-narrateur|Nino dit merci à maman.</t>
+          <t>narrateur|Un seau bleu est sous le banc.
+narrateur|La poule de papier reste dans le souvenir.
+narrateur|Nino a choisi la poule.
+narrateur|Puis les balançoires. Puis bleu.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient de la poule, et des balançoires.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15600,7 +16351,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin de la poule. Il a joué à les balançoires. Il a pris le bleu. Le seau bleu a dormi sous le banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15740,7 +16491,15 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin de la poule.
+narrateur|Il a joué à les balançoires.
+narrateur|Il a pris le bleu.
+narrateur|Le seau bleu a dormi sous le banc.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15768,7 +16527,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Nino montre vert. Maman a vu la poule. Et les balançoires. Ça sent le pain chaud. Nino ferme la porte, tout doux. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>Une craie verte trace un nid, pour de rire. La poule de papier a séché, tout calme. Nino a choisi la poule. Puis les balançoires. Puis vert. Le camarade a encore besoin de calme. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Merci, maman. Bravo, Nino. C'est du bon travail. La cour redevient calme, tout doux. Nino se souvient de la poule, et des balançoires.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15908,7 +16667,20 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Nino montre vert. Maman a vu la poule. Et les balançoires. Ça sent le pain chaud. Nino ferme la porte, tout doux. On peut répéter la règle. On peut observer d'abord. On répète. On attend. On laisse observer d'abord. Nino dit merci à maman.</t>
+          <t>narrateur|Une craie verte trace un nid, pour de rire.
+narrateur|La poule de papier a séché, tout calme.
+narrateur|Nino a choisi la poule.
+narrateur|Puis les balançoires. Puis vert.
+narrateur|Le camarade a encore besoin de calme.
+maman|On peut répéter la règle.
+papa|On peut observer d'abord.
+enfant-m|On répète. On attend.
+maman|On laisse observer d'abord.
+enfant-m|Merci, maman.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La cour redevient calme, tout doux.
+narrateur|Nino se souvient de la poule, et des balançoires.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15936,7 +16708,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai répété la règle. Il a observé d'abord. Bravo, Nino. Tu as fait du bon travail. Nino a visité le coin de la poule. Il a joué à les balançoires. Il a pris le vert. Le nid vert de craie reste au sol. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16076,7 +16848,15 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai répété la règle.
+enfant-m|Il a observé d'abord.
+maman|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino a visité le coin de la poule.
+narrateur|Il a joué à les balançoires.
+narrateur|Il a pris le vert.
+narrateur|Le nid vert de craie reste au sol.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16098,7 +16878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16192,6 +16972,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>
